--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:20</t>
+    <t xml:space="preserve">2026-09-09 18:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 18:58</t>
+    <t xml:space="preserve">2026-09-17 04:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:17</t>
+    <t xml:space="preserve">2026-09-25 11:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:10</t>
+    <t xml:space="preserve">2026-09-27 02:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_biobio_provincial.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Bíobío</t>
+    <t xml:space="preserve">Bío-Bío</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:07</t>
+    <t xml:space="preserve">2026-10-05 04:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Biobio</t>
+    <t xml:space="preserve">Region de Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
